--- a/uc13/MiniProjeto/_doc/Dicionario.xlsx
+++ b/uc13/MiniProjeto/_doc/Dicionario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MAMP\htdocs\t16\uc13\MiniProjeto\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC62611E-CAEA-49FC-8591-D6F1F60CBCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB17829-1503-4C1C-AE8F-A981FD35BEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F6AB9AB-1CB1-4A1B-8C7B-734A84488632}"/>
   </bookViews>
@@ -33,6 +33,242 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="77">
+  <si>
+    <t>Tabela</t>
+  </si>
+  <si>
+    <t>Chave</t>
+  </si>
+  <si>
+    <t>Campo</t>
+  </si>
+  <si>
+    <t>Tipo/Tamanho</t>
+  </si>
+  <si>
+    <t>Requerido</t>
+  </si>
+  <si>
+    <t>Regra</t>
+  </si>
+  <si>
+    <t>Obs</t>
+  </si>
+  <si>
+    <t>Usuario</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>id_usuario</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>not null</t>
+  </si>
+  <si>
+    <t>auto_increment primary key</t>
+  </si>
+  <si>
+    <t>nome_usuario</t>
+  </si>
+  <si>
+    <t>login_usuario</t>
+  </si>
+  <si>
+    <t>senha_usuario</t>
+  </si>
+  <si>
+    <t>foto_usuario</t>
+  </si>
+  <si>
+    <t>funcao_usuario</t>
+  </si>
+  <si>
+    <t>cad_usuario</t>
+  </si>
+  <si>
+    <t>obs_usuario</t>
+  </si>
+  <si>
+    <t>status_usuario</t>
+  </si>
+  <si>
+    <t>varchar(50)</t>
+  </si>
+  <si>
+    <t>varchar(30)</t>
+  </si>
+  <si>
+    <t>varchar(255)</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>unique</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>id_categoria</t>
+  </si>
+  <si>
+    <t>nome_categoria</t>
+  </si>
+  <si>
+    <t>descricao_categoria</t>
+  </si>
+  <si>
+    <t>obs_categoria</t>
+  </si>
+  <si>
+    <t>status_categoria</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>id_produto</t>
+  </si>
+  <si>
+    <t>FK</t>
+  </si>
+  <si>
+    <t>nome_produto</t>
+  </si>
+  <si>
+    <t>varchar(100)</t>
+  </si>
+  <si>
+    <t>valor_custo</t>
+  </si>
+  <si>
+    <t>decimal(10,2)</t>
+  </si>
+  <si>
+    <t>valor_venda</t>
+  </si>
+  <si>
+    <t>qtde_produto</t>
+  </si>
+  <si>
+    <t>obs_produto</t>
+  </si>
+  <si>
+    <t>status_produto</t>
+  </si>
+  <si>
+    <t>id_categoria_produto</t>
+  </si>
+  <si>
+    <t>id_movimentacao</t>
+  </si>
+  <si>
+    <t>id_usuario_movimentacao</t>
+  </si>
+  <si>
+    <t>id_produto_movimentacao</t>
+  </si>
+  <si>
+    <t>data_movimentacao</t>
+  </si>
+  <si>
+    <t>tipo_movimentacao</t>
+  </si>
+  <si>
+    <t>qtde_movimentacao</t>
+  </si>
+  <si>
+    <t>obs_movimentacao</t>
+  </si>
+  <si>
+    <t>status_movimentacao</t>
+  </si>
+  <si>
+    <t>Movimentacao</t>
+  </si>
+  <si>
+    <t>Tabela de Funcionário</t>
+  </si>
+  <si>
+    <t>have</t>
+  </si>
+  <si>
+    <t>id_fornecedor</t>
+  </si>
+  <si>
+    <t>nome_fornecedor</t>
+  </si>
+  <si>
+    <t>cnpj_fornecedor</t>
+  </si>
+  <si>
+    <t>varchar(18)</t>
+  </si>
+  <si>
+    <t>email_fornecedor</t>
+  </si>
+  <si>
+    <t>telefone_fornecedor</t>
+  </si>
+  <si>
+    <t>varchar(20)</t>
+  </si>
+  <si>
+    <t>obs_fornecedor</t>
+  </si>
+  <si>
+    <t>status_fornecedor</t>
+  </si>
+  <si>
+    <t>cad_fornecedor</t>
+  </si>
+  <si>
+    <t>endereco_rua</t>
+  </si>
+  <si>
+    <t>endereco_numero</t>
+  </si>
+  <si>
+    <t>varchar(10)</t>
+  </si>
+  <si>
+    <t>endereco_complemento</t>
+  </si>
+  <si>
+    <t>endereco_bairro</t>
+  </si>
+  <si>
+    <t>endereco_cidade</t>
+  </si>
+  <si>
+    <t>endereco_estado</t>
+  </si>
+  <si>
+    <t>varchar(2)</t>
+  </si>
+  <si>
+    <t>endereco_cep</t>
+  </si>
+  <si>
+    <t>varchar(9)</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +638,808 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B431D28-C719-4C0F-B2C5-9FA4FABDD17B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>74</v>
+      </c>
+      <c r="C56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/uc13/MiniProjeto/_doc/Dicionario.xlsx
+++ b/uc13/MiniProjeto/_doc/Dicionario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MAMP\htdocs\t16\uc13\MiniProjeto\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB17829-1503-4C1C-AE8F-A981FD35BEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D593FF1-A6A1-4C8D-8149-ACA4B31C8B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F6AB9AB-1CB1-4A1B-8C7B-734A84488632}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="77">
   <si>
     <t>Tabela</t>
   </si>
@@ -200,9 +200,6 @@
     <t>Movimentacao</t>
   </si>
   <si>
-    <t>Tabela de Funcionário</t>
-  </si>
-  <si>
     <t>have</t>
   </si>
   <si>
@@ -267,6 +264,9 @@
   </si>
   <si>
     <t>,</t>
+  </si>
+  <si>
+    <t>Funcionário</t>
   </si>
 </sst>
 </file>
@@ -692,7 +692,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -706,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -723,7 +723,7 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -737,7 +737,7 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -751,7 +751,7 @@
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -765,7 +765,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -779,7 +779,7 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -793,7 +793,7 @@
         <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
         <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -883,7 +883,7 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -897,7 +897,7 @@
         <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -956,7 +956,7 @@
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -973,7 +973,7 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -987,7 +987,7 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,7 +1001,7 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1015,7 +1015,7 @@
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1029,7 +1029,7 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1043,7 +1043,7 @@
         <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1099,7 +1099,7 @@
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1116,7 +1116,7 @@
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1133,7 +1133,7 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1147,7 +1147,7 @@
         <v>11</v>
       </c>
       <c r="F37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="F38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1175,7 +1175,7 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1189,7 +1189,7 @@
         <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1205,12 +1205,15 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
         <v>2</v>
@@ -1230,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
         <v>10</v>
@@ -1242,12 +1245,12 @@
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
         <v>37</v>
@@ -1256,26 +1259,26 @@
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
         <v>58</v>
       </c>
-      <c r="C47" t="s">
-        <v>59</v>
-      </c>
       <c r="D47" t="s">
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
         <v>37</v>
@@ -1284,26 +1287,26 @@
         <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" t="s">
         <v>61</v>
       </c>
-      <c r="C49" t="s">
-        <v>62</v>
-      </c>
       <c r="D49" t="s">
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C50" t="s">
         <v>37</v>
@@ -1312,26 +1315,26 @@
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" t="s">
         <v>67</v>
       </c>
-      <c r="C51" t="s">
-        <v>68</v>
-      </c>
       <c r="D51" t="s">
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
         <v>21</v>
@@ -1340,12 +1343,12 @@
         <v>11</v>
       </c>
       <c r="F52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
         <v>21</v>
@@ -1354,12 +1357,12 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
         <v>21</v>
@@ -1368,40 +1371,40 @@
         <v>11</v>
       </c>
       <c r="F54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" t="s">
         <v>72</v>
       </c>
-      <c r="C55" t="s">
-        <v>73</v>
-      </c>
       <c r="D55" t="s">
         <v>11</v>
       </c>
       <c r="F55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" t="s">
         <v>74</v>
       </c>
-      <c r="C56" t="s">
-        <v>75</v>
-      </c>
       <c r="D56" t="s">
         <v>11</v>
       </c>
       <c r="F56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
         <v>24</v>
@@ -1410,12 +1413,12 @@
         <v>11</v>
       </c>
       <c r="F57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
         <v>23</v>
@@ -1424,12 +1427,12 @@
         <v>25</v>
       </c>
       <c r="F58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
